--- a/LAB1/ZALACZNIKI/C1.xlsx
+++ b/LAB1/ZALACZNIKI/C1.xlsx
@@ -1,20 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bartoszzaborowski/Desktop/NotatkiPW/SEMESTR IV/TWM/LABKI/TWM_LABY_26L/LAB1/ZALACZNIKI/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71D0678-3F09-AA4C-8636-EEB0E53D8397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="34200" yWindow="600" windowWidth="11920" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Arkusz1"/>
+    <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Zespół</t>
   </si>
@@ -95,14 +114,25 @@
   </si>
   <si>
     <t>Dla odległości 3m</t>
+  </si>
+  <si>
+    <t>[4284; 5712]</t>
+  </si>
+  <si>
+    <t>0,0745 m/s</t>
+  </si>
+  <si>
+    <t>0,0497 m/s</t>
+  </si>
+  <si>
+    <t>0,0248 m/s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,8 +153,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,16 +170,34 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFcccccc"/>
+        <fgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeeeeee"/>
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -165,39 +220,126 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="dotted">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -208,10 +350,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -249,71 +391,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -341,7 +483,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -364,11 +506,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -377,13 +519,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -393,7 +535,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -402,7 +544,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -411,7 +553,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -419,10 +561,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -487,261 +629,234 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="6" width="52.86214285714286" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="30.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="52.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="3">
+        <v>4025.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
-      <c r="A10" s="4" t="s">
+      <c r="B9" s="3">
+        <v>4024.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="4" t="s">
+      <c r="B10" s="3">
+        <v>2845.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+      <c r="B11" s="3">
+        <v>2148.1999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
-      <c r="A14" s="5" t="s">
+      <c r="B13" s="3">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
-      <c r="A16" s="5" t="s">
+      <c r="B15" s="7">
+        <v>2289.1356999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
-      <c r="A17" s="4" t="s">
+      <c r="B16" s="14">
+        <f>($B$8*$B$13)/B15</f>
+        <v>42.554165749107838</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
-      <c r="A19" s="4" t="s">
+      <c r="B18" s="10">
+        <v>1070.0353</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
-      <c r="A20" s="5" t="s">
+      <c r="B19" s="15">
+        <f>($B$8*$B$13)/B18</f>
+        <v>91.036491973676007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="5" t="s">
+      <c r="B20" s="11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="5" t="s">
+      <c r="B21" s="12">
+        <v>630.04870000000005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="B22" s="16">
+        <f>($B$8*$B$13)/B21</f>
+        <v>154.6106832694044</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="5" t="s">
+      <c r="B23" s="13"/>
+    </row>
+    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="4" t="s">
+      <c r="B24" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="5"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="20.75">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="20.75">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="20.75">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="20.75">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="20.75">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="20.75">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="20.75">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="20.75">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="20.75">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="20.75">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="20.75">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="20.75">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="20.75">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="20.75">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="20.75">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="20.75">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="20.75">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="20.75">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="20.75">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="20.75">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="20.75">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-    </row>
+      <c r="B26" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LAB1/ZALACZNIKI/C1.xlsx
+++ b/LAB1/ZALACZNIKI/C1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bartoszzaborowski/Desktop/NotatkiPW/SEMESTR IV/TWM/LABKI/TWM_LABY_26L/LAB1/ZALACZNIKI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71D0678-3F09-AA4C-8636-EEB0E53D8397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFA86B0-656E-D548-B955-CDA808B95593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34200" yWindow="600" windowWidth="11920" windowHeight="17300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45100" yWindow="920" windowWidth="16700" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +196,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -278,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -328,6 +334,7 @@
     <xf numFmtId="2" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -633,7 +640,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.83203125" bestFit="1" customWidth="1"/>
@@ -756,7 +763,7 @@
         <v>42.554165749107838</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
@@ -764,7 +771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -772,7 +779,7 @@
         <v>1070.0353</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
@@ -781,7 +788,7 @@
         <v>91.036491973676007</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
@@ -789,7 +796,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
@@ -797,7 +804,7 @@
         <v>630.04870000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -806,42 +813,54 @@
         <v>154.6106832694044</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="13"/>
     </row>
-    <row r="24" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="17">
+        <f>1/($B$8*0.01)</f>
+        <v>2.4842868854495315E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="17">
+        <f>2/($B$8*0.01)</f>
+        <v>4.9685737708990631E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:2" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C26" s="17">
+        <f>3/($B$8*0.01)</f>
+        <v>7.452860656348595E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/LAB1/ZALACZNIKI/C1.xlsx
+++ b/LAB1/ZALACZNIKI/C1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bartoszzaborowski/Desktop/NotatkiPW/SEMESTR IV/TWM/LABKI/TWM_LABY_26L/LAB1/ZALACZNIKI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piotr\Desktop\STUDIA\sem4\TWM\TWM_LABY_26L\LAB1\ZALACZNIKI\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFA86B0-656E-D548-B955-CDA808B95593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45100" yWindow="920" windowWidth="16700" windowHeight="15660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -641,19 +641,19 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -661,7 +661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -669,14 +669,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2"/>
     </row>
-    <row r="6" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -684,7 +684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
@@ -692,7 +692,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -700,7 +700,7 @@
         <v>4025.3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -708,7 +708,7 @@
         <v>4024.8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -716,7 +716,7 @@
         <v>2845.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -724,13 +724,13 @@
         <v>2148.1999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
@@ -738,7 +738,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -746,7 +746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
@@ -754,7 +754,7 @@
         <v>2289.1356999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>16</v>
       </c>
@@ -763,7 +763,7 @@
         <v>42.554165749107838</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
@@ -771,7 +771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
@@ -779,7 +779,7 @@
         <v>1070.0353</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
@@ -788,7 +788,7 @@
         <v>91.036491973676007</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
@@ -796,7 +796,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
@@ -804,7 +804,7 @@
         <v>630.04870000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -813,13 +813,13 @@
         <v>154.6106832694044</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="13"/>
     </row>
-    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
@@ -831,7 +831,7 @@
         <v>2.4842868854495315E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
@@ -843,7 +843,7 @@
         <v>4.9685737708990631E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
@@ -855,27 +855,27 @@
         <v>7.452860656348595E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:3" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="20.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:3" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="20.85" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
